--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293066</v>
+        <v>122291892</v>
       </c>
       <c r="B2" t="n">
-        <v>58077</v>
+        <v>56266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338145</v>
+        <v>338212</v>
       </c>
       <c r="R2" t="n">
-        <v>6396569</v>
+        <v>6396580</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291911</v>
+        <v>122293618</v>
       </c>
       <c r="B3" t="n">
-        <v>56264</v>
+        <v>57708</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,42 +802,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338057</v>
+        <v>338112</v>
       </c>
       <c r="R3" t="n">
-        <v>6396357</v>
+        <v>6396514</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291890</v>
+        <v>122293944</v>
       </c>
       <c r="B4" t="n">
-        <v>56264</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +913,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338032</v>
+        <v>338069</v>
       </c>
       <c r="R4" t="n">
-        <v>6396372</v>
+        <v>6396358</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293055</v>
+        <v>122293941</v>
       </c>
       <c r="B5" t="n">
-        <v>58077</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338165</v>
+        <v>338163</v>
       </c>
       <c r="R5" t="n">
-        <v>6396568</v>
+        <v>6396611</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1091,12 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293038</v>
+        <v>122293066</v>
       </c>
       <c r="B6" t="n">
-        <v>58077</v>
+        <v>58079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338150</v>
+        <v>338145</v>
       </c>
       <c r="R6" t="n">
-        <v>6396559</v>
+        <v>6396569</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1206,12 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293618</v>
+        <v>122293055</v>
       </c>
       <c r="B7" t="n">
-        <v>57706</v>
+        <v>58079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1291,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338112</v>
+        <v>338165</v>
       </c>
       <c r="R7" t="n">
-        <v>6396514</v>
+        <v>6396568</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1357,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291889</v>
+        <v>122291911</v>
       </c>
       <c r="B8" t="n">
-        <v>56264</v>
+        <v>56266</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,13 +1406,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338067</v>
+        <v>338057</v>
       </c>
       <c r="R8" t="n">
-        <v>6396349</v>
+        <v>6396357</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,12 +1436,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,7 +1461,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1468,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291930</v>
+        <v>122291926</v>
       </c>
       <c r="B9" t="n">
-        <v>58232</v>
+        <v>58234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,7 +1517,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338059</v>
+        <v>338033</v>
       </c>
       <c r="R9" t="n">
-        <v>6396360</v>
+        <v>6396368</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,12 +1556,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,7 +1581,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1588,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291912</v>
+        <v>122291890</v>
       </c>
       <c r="B10" t="n">
-        <v>56264</v>
+        <v>56266</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,7 +1637,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338034</v>
+        <v>338032</v>
       </c>
       <c r="R10" t="n">
         <v>6396372</v>
@@ -1663,12 +1667,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1692,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1810,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293941</v>
+        <v>122291912</v>
       </c>
       <c r="B12" t="n">
-        <v>56824</v>
+        <v>56266</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,50 +1826,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338163</v>
+        <v>338034</v>
       </c>
       <c r="R12" t="n">
-        <v>6396611</v>
+        <v>6396372</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1925,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122293806</v>
+        <v>122291930</v>
       </c>
       <c r="B13" t="n">
-        <v>57914</v>
+        <v>58234</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,21 +1941,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102990</v>
+        <v>208249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1963,24 +1963,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338130</v>
+        <v>338059</v>
       </c>
       <c r="R13" t="n">
-        <v>6396548</v>
+        <v>6396360</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,12 +2009,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2034,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2040,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291926</v>
+        <v>122293038</v>
       </c>
       <c r="B14" t="n">
-        <v>58232</v>
+        <v>58079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,20 +2057,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2078,29 +2083,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338033</v>
+        <v>338150</v>
       </c>
       <c r="R14" t="n">
-        <v>6396368</v>
+        <v>6396559</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2160,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291892</v>
+        <v>122291889</v>
       </c>
       <c r="B15" t="n">
-        <v>56264</v>
+        <v>56266</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,14 +2201,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338212</v>
+        <v>338067</v>
       </c>
       <c r="R15" t="n">
-        <v>6396580</v>
+        <v>6396349</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122293944</v>
+        <v>122293806</v>
       </c>
       <c r="B16" t="n">
-        <v>56824</v>
+        <v>57916</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,16 +2287,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2311,22 +2311,22 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338069</v>
+        <v>338130</v>
       </c>
       <c r="R16" t="n">
-        <v>6396358</v>
+        <v>6396548</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291892</v>
+        <v>122291889</v>
       </c>
       <c r="B2" t="n">
         <v>56266</v>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338212</v>
+        <v>338067</v>
       </c>
       <c r="R2" t="n">
-        <v>6396580</v>
+        <v>6396349</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293618</v>
+        <v>122291953</v>
       </c>
       <c r="B3" t="n">
-        <v>57708</v>
+        <v>8425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338112</v>
+        <v>338171</v>
       </c>
       <c r="R3" t="n">
-        <v>6396514</v>
+        <v>6396632</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293944</v>
+        <v>122293806</v>
       </c>
       <c r="B4" t="n">
-        <v>56826</v>
+        <v>57916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -941,22 +937,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338069</v>
+        <v>338130</v>
       </c>
       <c r="R4" t="n">
-        <v>6396358</v>
+        <v>6396548</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293941</v>
+        <v>122293038</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>58079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1024,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1065,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338163</v>
+        <v>338150</v>
       </c>
       <c r="R5" t="n">
-        <v>6396611</v>
+        <v>6396559</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1095,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293066</v>
+        <v>122293055</v>
       </c>
       <c r="B6" t="n">
         <v>58079</v>
@@ -1180,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338145</v>
+        <v>338165</v>
       </c>
       <c r="R6" t="n">
-        <v>6396569</v>
+        <v>6396568</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1210,12 +1206,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293055</v>
+        <v>122291890</v>
       </c>
       <c r="B7" t="n">
-        <v>58079</v>
+        <v>56266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,46 +1258,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338165</v>
+        <v>338032</v>
       </c>
       <c r="R7" t="n">
-        <v>6396568</v>
+        <v>6396372</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,12 +1317,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1342,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1361,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291911</v>
+        <v>122293944</v>
       </c>
       <c r="B8" t="n">
-        <v>56266</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,31 +1365,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1406,13 +1402,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338057</v>
+        <v>338069</v>
       </c>
       <c r="R8" t="n">
-        <v>6396357</v>
+        <v>6396358</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,12 +1432,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1457,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1472,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291926</v>
+        <v>122291912</v>
       </c>
       <c r="B9" t="n">
-        <v>58234</v>
+        <v>56266</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,40 +1480,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,13 +1513,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338033</v>
+        <v>338034</v>
       </c>
       <c r="R9" t="n">
-        <v>6396368</v>
+        <v>6396372</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,12 +1543,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1568,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1592,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291890</v>
+        <v>122291926</v>
       </c>
       <c r="B10" t="n">
-        <v>56266</v>
+        <v>58234</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,31 +1591,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1637,13 +1633,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338032</v>
+        <v>338033</v>
       </c>
       <c r="R10" t="n">
-        <v>6396372</v>
+        <v>6396368</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,12 +1663,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291953</v>
+        <v>122293941</v>
       </c>
       <c r="B11" t="n">
-        <v>8425</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,27 +1715,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338171</v>
+        <v>338163</v>
       </c>
       <c r="R11" t="n">
-        <v>6396632</v>
+        <v>6396611</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291912</v>
+        <v>122293618</v>
       </c>
       <c r="B12" t="n">
-        <v>56266</v>
+        <v>57708</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,42 +1830,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>103008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338034</v>
+        <v>338112</v>
       </c>
       <c r="R12" t="n">
-        <v>6396372</v>
+        <v>6396514</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,12 +1893,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,7 +1918,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2045,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122293038</v>
+        <v>122291892</v>
       </c>
       <c r="B14" t="n">
-        <v>58079</v>
+        <v>56266</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,31 +2065,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338150</v>
+        <v>338212</v>
       </c>
       <c r="R14" t="n">
-        <v>6396559</v>
+        <v>6396580</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2160,7 +2160,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291889</v>
+        <v>122291911</v>
       </c>
       <c r="B15" t="n">
         <v>56266</v>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338067</v>
+        <v>338057</v>
       </c>
       <c r="R15" t="n">
-        <v>6396349</v>
+        <v>6396357</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122293806</v>
+        <v>122293066</v>
       </c>
       <c r="B16" t="n">
-        <v>57916</v>
+        <v>58079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338130</v>
+        <v>338145</v>
       </c>
       <c r="R16" t="n">
-        <v>6396548</v>
+        <v>6396569</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291890</v>
+        <v>122293618</v>
       </c>
       <c r="B2" t="n">
-        <v>56266</v>
+        <v>57708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338032</v>
+        <v>338112</v>
       </c>
       <c r="R2" t="n">
-        <v>6396372</v>
+        <v>6396514</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293944</v>
+        <v>122291926</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>58234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,9 +828,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338069</v>
+        <v>338033</v>
       </c>
       <c r="R3" t="n">
-        <v>6396358</v>
+        <v>6396368</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293941</v>
+        <v>122291930</v>
       </c>
       <c r="B4" t="n">
-        <v>56826</v>
+        <v>58234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,24 +948,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338163</v>
+        <v>338059</v>
       </c>
       <c r="R4" t="n">
-        <v>6396611</v>
+        <v>6396360</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1019,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293806</v>
+        <v>122291889</v>
       </c>
       <c r="B5" t="n">
-        <v>57916</v>
+        <v>56266</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,50 +1042,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338130</v>
+        <v>338067</v>
       </c>
       <c r="R5" t="n">
-        <v>6396548</v>
+        <v>6396349</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1105,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1130,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293066</v>
+        <v>122291892</v>
       </c>
       <c r="B6" t="n">
-        <v>58079</v>
+        <v>56266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,31 +1157,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1180,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338145</v>
+        <v>338212</v>
       </c>
       <c r="R6" t="n">
-        <v>6396569</v>
+        <v>6396580</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,12 +1216,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1241,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1246,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291926</v>
+        <v>122293941</v>
       </c>
       <c r="B7" t="n">
-        <v>58234</v>
+        <v>56826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1284,29 +1290,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338033</v>
+        <v>338163</v>
       </c>
       <c r="R7" t="n">
-        <v>6396368</v>
+        <v>6396611</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1356,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1481,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293618</v>
+        <v>122293066</v>
       </c>
       <c r="B9" t="n">
-        <v>57708</v>
+        <v>58079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1530,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338112</v>
+        <v>338145</v>
       </c>
       <c r="R9" t="n">
-        <v>6396514</v>
+        <v>6396569</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1560,12 +1561,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291930</v>
+        <v>122291953</v>
       </c>
       <c r="B10" t="n">
-        <v>58234</v>
+        <v>8425</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,51 +1613,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338059</v>
+        <v>338171</v>
       </c>
       <c r="R10" t="n">
-        <v>6396360</v>
+        <v>6396632</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,12 +1672,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293055</v>
+        <v>122291911</v>
       </c>
       <c r="B11" t="n">
-        <v>58079</v>
+        <v>56266</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,46 +1724,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338165</v>
+        <v>338057</v>
       </c>
       <c r="R11" t="n">
-        <v>6396568</v>
+        <v>6396357</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,12 +1783,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1808,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1831,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291912</v>
+        <v>122293944</v>
       </c>
       <c r="B12" t="n">
-        <v>56266</v>
+        <v>56826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,31 +1831,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1876,13 +1868,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338034</v>
+        <v>338069</v>
       </c>
       <c r="R12" t="n">
-        <v>6396372</v>
+        <v>6396358</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,7 +1923,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1942,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291892</v>
+        <v>122293055</v>
       </c>
       <c r="B13" t="n">
-        <v>56266</v>
+        <v>58079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,27 +1950,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1987,13 +1983,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338212</v>
+        <v>338165</v>
       </c>
       <c r="R13" t="n">
-        <v>6396580</v>
+        <v>6396568</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,12 +2013,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,7 +2038,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2053,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291953</v>
+        <v>122293806</v>
       </c>
       <c r="B14" t="n">
-        <v>8425</v>
+        <v>57916</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,27 +2065,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338171</v>
+        <v>338130</v>
       </c>
       <c r="R14" t="n">
-        <v>6396632</v>
+        <v>6396548</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2164,7 +2164,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291911</v>
+        <v>122291912</v>
       </c>
       <c r="B15" t="n">
         <v>56266</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338057</v>
+        <v>338034</v>
       </c>
       <c r="R15" t="n">
-        <v>6396357</v>
+        <v>6396372</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2275,7 +2275,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291889</v>
+        <v>122291890</v>
       </c>
       <c r="B16" t="n">
         <v>56266</v>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338067</v>
+        <v>338032</v>
       </c>
       <c r="R16" t="n">
-        <v>6396349</v>
+        <v>6396372</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293618</v>
+        <v>122293941</v>
       </c>
       <c r="B2" t="n">
-        <v>57708</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338112</v>
+        <v>338163</v>
       </c>
       <c r="R2" t="n">
-        <v>6396514</v>
+        <v>6396611</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291926</v>
+        <v>122291889</v>
       </c>
       <c r="B3" t="n">
-        <v>58234</v>
+        <v>56266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,40 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338033</v>
+        <v>338067</v>
       </c>
       <c r="R3" t="n">
-        <v>6396368</v>
+        <v>6396349</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291930</v>
+        <v>122291912</v>
       </c>
       <c r="B4" t="n">
-        <v>58234</v>
+        <v>56266</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,40 +913,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338059</v>
+        <v>338034</v>
       </c>
       <c r="R4" t="n">
-        <v>6396360</v>
+        <v>6396372</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291889</v>
+        <v>122293066</v>
       </c>
       <c r="B5" t="n">
-        <v>56266</v>
+        <v>58079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,42 +1028,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338067</v>
+        <v>338145</v>
       </c>
       <c r="R5" t="n">
-        <v>6396349</v>
+        <v>6396569</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1141,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291892</v>
+        <v>122291911</v>
       </c>
       <c r="B6" t="n">
         <v>56266</v>
@@ -1182,17 +1168,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338212</v>
+        <v>338057</v>
       </c>
       <c r="R6" t="n">
-        <v>6396580</v>
+        <v>6396357</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,12 +1202,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,7 +1227,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1252,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293941</v>
+        <v>122293806</v>
       </c>
       <c r="B7" t="n">
-        <v>56826</v>
+        <v>57916</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,16 +1254,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1301,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338163</v>
+        <v>338130</v>
       </c>
       <c r="R7" t="n">
-        <v>6396611</v>
+        <v>6396548</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1331,12 +1317,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293038</v>
+        <v>122291890</v>
       </c>
       <c r="B8" t="n">
-        <v>58079</v>
+        <v>56266</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,46 +1369,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338150</v>
+        <v>338032</v>
       </c>
       <c r="R8" t="n">
-        <v>6396559</v>
+        <v>6396372</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1428,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1453,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1482,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293066</v>
+        <v>122293618</v>
       </c>
       <c r="B9" t="n">
-        <v>58079</v>
+        <v>57708</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338145</v>
+        <v>338112</v>
       </c>
       <c r="R9" t="n">
-        <v>6396569</v>
+        <v>6396514</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1561,12 +1543,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291953</v>
+        <v>122291930</v>
       </c>
       <c r="B10" t="n">
-        <v>8425</v>
+        <v>58234</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,42 +1595,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338171</v>
+        <v>338059</v>
       </c>
       <c r="R10" t="n">
-        <v>6396632</v>
+        <v>6396360</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,12 +1663,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291911</v>
+        <v>122293055</v>
       </c>
       <c r="B11" t="n">
-        <v>56266</v>
+        <v>58079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,42 +1715,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338057</v>
+        <v>338165</v>
       </c>
       <c r="R11" t="n">
-        <v>6396357</v>
+        <v>6396568</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,12 +1778,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1803,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1819,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293944</v>
+        <v>122291926</v>
       </c>
       <c r="B12" t="n">
-        <v>56826</v>
+        <v>58234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,21 +1830,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>208249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1857,9 +1852,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338069</v>
+        <v>338033</v>
       </c>
       <c r="R12" t="n">
-        <v>6396358</v>
+        <v>6396368</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122293055</v>
+        <v>122293038</v>
       </c>
       <c r="B13" t="n">
         <v>58079</v>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338165</v>
+        <v>338150</v>
       </c>
       <c r="R13" t="n">
-        <v>6396568</v>
+        <v>6396559</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122293806</v>
+        <v>122293944</v>
       </c>
       <c r="B14" t="n">
-        <v>57916</v>
+        <v>56826</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,16 +2065,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2089,22 +2089,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338130</v>
+        <v>338069</v>
       </c>
       <c r="R14" t="n">
-        <v>6396548</v>
+        <v>6396358</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291912</v>
+        <v>122291953</v>
       </c>
       <c r="B15" t="n">
-        <v>56266</v>
+        <v>8425</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,43 +2176,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338034</v>
+        <v>338171</v>
       </c>
       <c r="R15" t="n">
-        <v>6396372</v>
+        <v>6396632</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291890</v>
+        <v>122291892</v>
       </c>
       <c r="B16" t="n">
         <v>56266</v>
@@ -2316,17 +2316,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338032</v>
+        <v>338212</v>
       </c>
       <c r="R16" t="n">
-        <v>6396372</v>
+        <v>6396580</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293941</v>
+        <v>122293618</v>
       </c>
       <c r="B2" t="n">
-        <v>56826</v>
+        <v>57708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338163</v>
+        <v>338112</v>
       </c>
       <c r="R2" t="n">
-        <v>6396611</v>
+        <v>6396514</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291889</v>
+        <v>122293055</v>
       </c>
       <c r="B3" t="n">
-        <v>56266</v>
+        <v>58079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,42 +806,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338067</v>
+        <v>338165</v>
       </c>
       <c r="R3" t="n">
-        <v>6396349</v>
+        <v>6396568</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +894,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291912</v>
+        <v>122291926</v>
       </c>
       <c r="B4" t="n">
-        <v>56266</v>
+        <v>58234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +917,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338034</v>
+        <v>338033</v>
       </c>
       <c r="R4" t="n">
-        <v>6396372</v>
+        <v>6396368</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293066</v>
+        <v>122291912</v>
       </c>
       <c r="B5" t="n">
-        <v>58079</v>
+        <v>56266</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1041,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338145</v>
+        <v>338034</v>
       </c>
       <c r="R5" t="n">
-        <v>6396569</v>
+        <v>6396372</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1127,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291911</v>
+        <v>122293038</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>58079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,42 +1152,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338057</v>
+        <v>338150</v>
       </c>
       <c r="R6" t="n">
-        <v>6396357</v>
+        <v>6396559</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1238,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293806</v>
+        <v>122291953</v>
       </c>
       <c r="B7" t="n">
-        <v>57916</v>
+        <v>8425</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,31 +1267,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1287,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338130</v>
+        <v>338171</v>
       </c>
       <c r="R7" t="n">
-        <v>6396548</v>
+        <v>6396632</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,12 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,7 +1351,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1353,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291890</v>
+        <v>122291911</v>
       </c>
       <c r="B8" t="n">
         <v>56266</v>
@@ -1398,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338032</v>
+        <v>338057</v>
       </c>
       <c r="R8" t="n">
-        <v>6396372</v>
+        <v>6396357</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1428,12 +1437,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,7 +1462,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1464,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293618</v>
+        <v>122291890</v>
       </c>
       <c r="B9" t="n">
-        <v>57708</v>
+        <v>56266</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,46 +1489,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338112</v>
+        <v>338032</v>
       </c>
       <c r="R9" t="n">
-        <v>6396514</v>
+        <v>6396372</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1699,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293055</v>
+        <v>122293806</v>
       </c>
       <c r="B11" t="n">
-        <v>58079</v>
+        <v>57916</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,25 +1716,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1748,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338165</v>
+        <v>338130</v>
       </c>
       <c r="R11" t="n">
-        <v>6396568</v>
+        <v>6396548</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1814,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291926</v>
+        <v>122293941</v>
       </c>
       <c r="B12" t="n">
-        <v>58234</v>
+        <v>56826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,21 +1835,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1852,29 +1857,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338033</v>
+        <v>338163</v>
       </c>
       <c r="R12" t="n">
-        <v>6396368</v>
+        <v>6396611</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122293038</v>
+        <v>122293944</v>
       </c>
       <c r="B13" t="n">
-        <v>58079</v>
+        <v>56826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,25 +1946,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1974,22 +1974,22 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338150</v>
+        <v>338069</v>
       </c>
       <c r="R13" t="n">
-        <v>6396559</v>
+        <v>6396358</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122293944</v>
+        <v>122293066</v>
       </c>
       <c r="B14" t="n">
-        <v>56826</v>
+        <v>58079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,25 +2061,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2089,22 +2089,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338069</v>
+        <v>338145</v>
       </c>
       <c r="R14" t="n">
-        <v>6396358</v>
+        <v>6396569</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291953</v>
+        <v>122291892</v>
       </c>
       <c r="B15" t="n">
-        <v>8425</v>
+        <v>56266</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,31 +2176,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2209,13 +2209,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338171</v>
+        <v>338212</v>
       </c>
       <c r="R15" t="n">
-        <v>6396632</v>
+        <v>6396580</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291892</v>
+        <v>122291889</v>
       </c>
       <c r="B16" t="n">
         <v>56266</v>
@@ -2316,14 +2316,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338212</v>
+        <v>338067</v>
       </c>
       <c r="R16" t="n">
-        <v>6396580</v>
+        <v>6396349</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291890</v>
+        <v>122293806</v>
       </c>
       <c r="B9" t="n">
-        <v>56266</v>
+        <v>57916</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,46 +1485,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338032</v>
+        <v>338130</v>
       </c>
       <c r="R9" t="n">
-        <v>6396372</v>
+        <v>6396548</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,12 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,7 +1577,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1584,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291930</v>
+        <v>122293941</v>
       </c>
       <c r="B10" t="n">
-        <v>58234</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1604,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>102954</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1622,29 +1626,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338059</v>
+        <v>338163</v>
       </c>
       <c r="R10" t="n">
-        <v>6396360</v>
+        <v>6396611</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,12 +1667,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1692,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1704,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293806</v>
+        <v>122291890</v>
       </c>
       <c r="B11" t="n">
-        <v>57916</v>
+        <v>56266</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,50 +1715,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338130</v>
+        <v>338032</v>
       </c>
       <c r="R11" t="n">
-        <v>6396548</v>
+        <v>6396372</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,12 +1778,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1803,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1819,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293941</v>
+        <v>122291930</v>
       </c>
       <c r="B12" t="n">
-        <v>56826</v>
+        <v>58234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,21 +1830,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>208249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1857,24 +1852,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338163</v>
+        <v>338059</v>
       </c>
       <c r="R12" t="n">
-        <v>6396611</v>
+        <v>6396360</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293618</v>
+        <v>122293038</v>
       </c>
       <c r="B2" t="n">
-        <v>57708</v>
+        <v>58084</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338112</v>
+        <v>338150</v>
       </c>
       <c r="R2" t="n">
-        <v>6396514</v>
+        <v>6396559</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293055</v>
+        <v>122291911</v>
       </c>
       <c r="B3" t="n">
-        <v>58079</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,46 +806,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338165</v>
+        <v>338057</v>
       </c>
       <c r="R3" t="n">
-        <v>6396568</v>
+        <v>6396357</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291926</v>
+        <v>122291930</v>
       </c>
       <c r="B4" t="n">
-        <v>58234</v>
+        <v>58239</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,7 +946,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338033</v>
+        <v>338059</v>
       </c>
       <c r="R4" t="n">
-        <v>6396368</v>
+        <v>6396360</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291912</v>
+        <v>122293944</v>
       </c>
       <c r="B5" t="n">
-        <v>56266</v>
+        <v>56831</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,31 +1033,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338034</v>
+        <v>338069</v>
       </c>
       <c r="R5" t="n">
-        <v>6396372</v>
+        <v>6396358</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293038</v>
+        <v>122293806</v>
       </c>
       <c r="B6" t="n">
-        <v>58079</v>
+        <v>57921</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,25 +1148,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338150</v>
+        <v>338130</v>
       </c>
       <c r="R6" t="n">
-        <v>6396559</v>
+        <v>6396548</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291953</v>
+        <v>122293618</v>
       </c>
       <c r="B7" t="n">
-        <v>8425</v>
+        <v>57713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,31 +1263,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1296,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338171</v>
+        <v>338112</v>
       </c>
       <c r="R7" t="n">
-        <v>6396632</v>
+        <v>6396514</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,12 +1330,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1355,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1362,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291911</v>
+        <v>122291889</v>
       </c>
       <c r="B8" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338057</v>
+        <v>338067</v>
       </c>
       <c r="R8" t="n">
-        <v>6396357</v>
+        <v>6396349</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,12 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1466,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1473,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293806</v>
+        <v>122293941</v>
       </c>
       <c r="B9" t="n">
-        <v>57916</v>
+        <v>56831</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,16 +1493,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1522,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338130</v>
+        <v>338163</v>
       </c>
       <c r="R9" t="n">
-        <v>6396548</v>
+        <v>6396611</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1552,12 +1556,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122293941</v>
+        <v>122291890</v>
       </c>
       <c r="B10" t="n">
-        <v>56826</v>
+        <v>56271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,50 +1604,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338163</v>
+        <v>338032</v>
       </c>
       <c r="R10" t="n">
-        <v>6396611</v>
+        <v>6396372</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291890</v>
+        <v>122291953</v>
       </c>
       <c r="B11" t="n">
-        <v>56266</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,43 +1715,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338032</v>
+        <v>338171</v>
       </c>
       <c r="R11" t="n">
-        <v>6396372</v>
+        <v>6396632</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291930</v>
+        <v>122293055</v>
       </c>
       <c r="B12" t="n">
-        <v>58234</v>
+        <v>58084</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,20 +1826,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1852,29 +1852,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338059</v>
+        <v>338165</v>
       </c>
       <c r="R12" t="n">
-        <v>6396360</v>
+        <v>6396568</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,12 +1893,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,7 +1918,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1934,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122293944</v>
+        <v>122291912</v>
       </c>
       <c r="B13" t="n">
-        <v>56826</v>
+        <v>56271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,35 +1941,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1983,13 +1974,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338069</v>
+        <v>338034</v>
       </c>
       <c r="R13" t="n">
-        <v>6396358</v>
+        <v>6396372</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,12 +2004,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,7 +2029,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2052,7 +2043,7 @@
         <v>122293066</v>
       </c>
       <c r="B14" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2167,7 +2158,7 @@
         <v>122291892</v>
       </c>
       <c r="B15" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2275,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291889</v>
+        <v>122291926</v>
       </c>
       <c r="B16" t="n">
-        <v>56266</v>
+        <v>58239</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,31 +2278,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338067</v>
+        <v>338033</v>
       </c>
       <c r="R16" t="n">
-        <v>6396349</v>
+        <v>6396368</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293038</v>
+        <v>122293941</v>
       </c>
       <c r="B2" t="n">
-        <v>58084</v>
+        <v>56831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338150</v>
+        <v>338163</v>
       </c>
       <c r="R2" t="n">
-        <v>6396559</v>
+        <v>6396611</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291930</v>
+        <v>122291912</v>
       </c>
       <c r="B4" t="n">
-        <v>58239</v>
+        <v>56271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,40 +913,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -955,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338059</v>
+        <v>338034</v>
       </c>
       <c r="R4" t="n">
-        <v>6396360</v>
+        <v>6396372</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293944</v>
+        <v>122293806</v>
       </c>
       <c r="B5" t="n">
-        <v>56831</v>
+        <v>57921</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,16 +1028,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,22 +1052,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338069</v>
+        <v>338130</v>
       </c>
       <c r="R5" t="n">
-        <v>6396358</v>
+        <v>6396548</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293806</v>
+        <v>122291930</v>
       </c>
       <c r="B6" t="n">
-        <v>57921</v>
+        <v>58239</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1174,24 +1165,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338130</v>
+        <v>338059</v>
       </c>
       <c r="R6" t="n">
-        <v>6396548</v>
+        <v>6396360</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,12 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1236,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1251,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293618</v>
+        <v>122291953</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>8430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,35 +1259,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103008</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338112</v>
+        <v>338171</v>
       </c>
       <c r="R7" t="n">
-        <v>6396514</v>
+        <v>6396632</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,12 +1322,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1347,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1366,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291889</v>
+        <v>122291892</v>
       </c>
       <c r="B8" t="n">
         <v>56271</v>
@@ -1407,14 +1399,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338067</v>
+        <v>338212</v>
       </c>
       <c r="R8" t="n">
-        <v>6396349</v>
+        <v>6396580</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1477,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293941</v>
+        <v>122293618</v>
       </c>
       <c r="B9" t="n">
-        <v>56831</v>
+        <v>57713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,20 +1481,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102954</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1526,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338163</v>
+        <v>338112</v>
       </c>
       <c r="R9" t="n">
-        <v>6396611</v>
+        <v>6396514</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1556,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291890</v>
+        <v>122293038</v>
       </c>
       <c r="B10" t="n">
-        <v>56271</v>
+        <v>58084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,42 +1600,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338032</v>
+        <v>338150</v>
       </c>
       <c r="R10" t="n">
-        <v>6396372</v>
+        <v>6396559</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,12 +1663,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1688,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1703,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291953</v>
+        <v>122291889</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>56271</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,46 +1711,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338171</v>
+        <v>338067</v>
       </c>
       <c r="R11" t="n">
-        <v>6396632</v>
+        <v>6396349</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,12 +1774,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1799,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1814,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293055</v>
+        <v>122293944</v>
       </c>
       <c r="B12" t="n">
-        <v>58084</v>
+        <v>56831</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,25 +1822,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1854,22 +1850,22 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338165</v>
+        <v>338069</v>
       </c>
       <c r="R12" t="n">
-        <v>6396568</v>
+        <v>6396358</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1893,12 +1889,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291912</v>
+        <v>122293066</v>
       </c>
       <c r="B13" t="n">
-        <v>56271</v>
+        <v>58084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,42 +1941,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338034</v>
+        <v>338145</v>
       </c>
       <c r="R13" t="n">
-        <v>6396372</v>
+        <v>6396569</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2040,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122293066</v>
+        <v>122291890</v>
       </c>
       <c r="B14" t="n">
-        <v>58084</v>
+        <v>56271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,46 +2056,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338145</v>
+        <v>338032</v>
       </c>
       <c r="R14" t="n">
-        <v>6396569</v>
+        <v>6396372</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2119,12 +2115,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2140,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2155,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291892</v>
+        <v>122293055</v>
       </c>
       <c r="B15" t="n">
-        <v>56271</v>
+        <v>58084</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,27 +2167,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338212</v>
+        <v>338165</v>
       </c>
       <c r="R15" t="n">
-        <v>6396580</v>
+        <v>6396568</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291912</v>
+        <v>122293806</v>
       </c>
       <c r="B4" t="n">
-        <v>56271</v>
+        <v>57921</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,46 +913,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338034</v>
+        <v>338130</v>
       </c>
       <c r="R4" t="n">
-        <v>6396372</v>
+        <v>6396548</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293806</v>
+        <v>122291912</v>
       </c>
       <c r="B5" t="n">
-        <v>57921</v>
+        <v>56271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,50 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338130</v>
+        <v>338034</v>
       </c>
       <c r="R5" t="n">
-        <v>6396548</v>
+        <v>6396372</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -2040,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291890</v>
+        <v>122293055</v>
       </c>
       <c r="B14" t="n">
-        <v>56271</v>
+        <v>58084</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,42 +2056,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338032</v>
+        <v>338165</v>
       </c>
       <c r="R14" t="n">
-        <v>6396372</v>
+        <v>6396568</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,12 +2119,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,7 +2144,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2151,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122293055</v>
+        <v>122291890</v>
       </c>
       <c r="B15" t="n">
-        <v>58084</v>
+        <v>56271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,46 +2171,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338165</v>
+        <v>338032</v>
       </c>
       <c r="R15" t="n">
-        <v>6396568</v>
+        <v>6396372</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293806</v>
+        <v>122291912</v>
       </c>
       <c r="B4" t="n">
-        <v>57921</v>
+        <v>56271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,50 +913,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338130</v>
+        <v>338034</v>
       </c>
       <c r="R4" t="n">
-        <v>6396548</v>
+        <v>6396372</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291912</v>
+        <v>122293806</v>
       </c>
       <c r="B5" t="n">
-        <v>56271</v>
+        <v>57921</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1024,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338034</v>
+        <v>338130</v>
       </c>
       <c r="R5" t="n">
-        <v>6396372</v>
+        <v>6396548</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -2040,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122293055</v>
+        <v>122291890</v>
       </c>
       <c r="B14" t="n">
-        <v>58084</v>
+        <v>56271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,46 +2056,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338165</v>
+        <v>338032</v>
       </c>
       <c r="R14" t="n">
-        <v>6396568</v>
+        <v>6396372</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2119,12 +2115,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2140,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2155,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291890</v>
+        <v>122293055</v>
       </c>
       <c r="B15" t="n">
-        <v>56271</v>
+        <v>58084</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,42 +2167,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338032</v>
+        <v>338165</v>
       </c>
       <c r="R15" t="n">
-        <v>6396372</v>
+        <v>6396568</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293941</v>
+        <v>122291889</v>
       </c>
       <c r="B2" t="n">
-        <v>56831</v>
+        <v>56271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Enkelbeckasin</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338163</v>
+        <v>338067</v>
       </c>
       <c r="R2" t="n">
-        <v>6396611</v>
+        <v>6396349</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291911</v>
+        <v>122293066</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>58084</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,42 +797,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>103055</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338057</v>
+        <v>338145</v>
       </c>
       <c r="R3" t="n">
-        <v>6396357</v>
+        <v>6396569</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291912</v>
+        <v>122293944</v>
       </c>
       <c r="B4" t="n">
-        <v>56271</v>
+        <v>56831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +903,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>102954</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338034</v>
+        <v>338069</v>
       </c>
       <c r="R4" t="n">
-        <v>6396372</v>
+        <v>6396358</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293806</v>
+        <v>122293618</v>
       </c>
       <c r="B5" t="n">
-        <v>57921</v>
+        <v>57713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,20 +1013,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
+        <v>103008</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338130</v>
+        <v>338112</v>
       </c>
       <c r="R5" t="n">
-        <v>6396548</v>
+        <v>6396514</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1145,11 +1129,6 @@
       <c r="E6" t="n">
         <v>208249</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Rana temporaria</t>
@@ -1247,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291953</v>
+        <v>122291911</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>56271</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,43 +1238,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338171</v>
+        <v>338057</v>
       </c>
       <c r="R7" t="n">
-        <v>6396632</v>
+        <v>6396357</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1322,12 +1296,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291892</v>
+        <v>122293055</v>
       </c>
       <c r="B8" t="n">
-        <v>56271</v>
+        <v>58084</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,27 +1348,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>103055</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1403,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338212</v>
+        <v>338165</v>
       </c>
       <c r="R8" t="n">
-        <v>6396580</v>
+        <v>6396568</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,12 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1431,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1469,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293618</v>
+        <v>122291890</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>56271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,46 +1458,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ärtsångare</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338112</v>
+        <v>338032</v>
       </c>
       <c r="R9" t="n">
-        <v>6396514</v>
+        <v>6396372</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,12 +1512,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,7 +1537,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1584,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122293038</v>
+        <v>122293941</v>
       </c>
       <c r="B10" t="n">
-        <v>58084</v>
+        <v>56831</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,25 +1560,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
+        <v>102954</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1633,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338150</v>
+        <v>338163</v>
       </c>
       <c r="R10" t="n">
-        <v>6396559</v>
+        <v>6396611</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1663,12 +1622,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291889</v>
+        <v>122293806</v>
       </c>
       <c r="B11" t="n">
-        <v>56271</v>
+        <v>57921</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,46 +1670,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>102990</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338067</v>
+        <v>338130</v>
       </c>
       <c r="R11" t="n">
-        <v>6396349</v>
+        <v>6396548</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,12 +1732,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,7 +1757,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1810,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293944</v>
+        <v>122291926</v>
       </c>
       <c r="B12" t="n">
-        <v>56831</v>
+        <v>58239</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,21 +1784,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Enkelbeckasin</t>
-        </is>
+        <v>208249</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1848,9 +1801,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1859,13 +1817,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338069</v>
+        <v>338033</v>
       </c>
       <c r="R12" t="n">
-        <v>6396358</v>
+        <v>6396368</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,12 +1847,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,7 +1872,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1925,7 +1883,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122293066</v>
+        <v>122293038</v>
       </c>
       <c r="B13" t="n">
         <v>58084</v>
@@ -1943,11 +1901,6 @@
       <c r="E13" t="n">
         <v>103055</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Emberiza citrinella</t>
@@ -1974,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338145</v>
+        <v>338150</v>
       </c>
       <c r="R13" t="n">
-        <v>6396569</v>
+        <v>6396559</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2004,12 +1957,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,7 +1993,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291890</v>
+        <v>122291892</v>
       </c>
       <c r="B14" t="n">
         <v>56271</v>
@@ -2058,11 +2011,6 @@
       <c r="E14" t="n">
         <v>205998</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -2081,17 +2029,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338032</v>
+        <v>338212</v>
       </c>
       <c r="R14" t="n">
-        <v>6396372</v>
+        <v>6396580</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2151,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122293055</v>
+        <v>122291912</v>
       </c>
       <c r="B15" t="n">
-        <v>58084</v>
+        <v>56271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,46 +2115,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338165</v>
+        <v>338034</v>
       </c>
       <c r="R15" t="n">
-        <v>6396568</v>
+        <v>6396372</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,12 +2169,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2194,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2266,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291926</v>
+        <v>122291953</v>
       </c>
       <c r="B16" t="n">
-        <v>58239</v>
+        <v>8430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,51 +2221,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
+        <v>106554</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338033</v>
+        <v>338171</v>
       </c>
       <c r="R16" t="n">
-        <v>6396368</v>
+        <v>6396632</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2375,7 +2300,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293618</v>
+        <v>122291930</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>58239</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,20 +1013,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>208249</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1034,24 +1034,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338112</v>
+        <v>338059</v>
       </c>
       <c r="R5" t="n">
-        <v>6396514</v>
+        <v>6396360</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,7 +1105,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1111,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291930</v>
+        <v>122293618</v>
       </c>
       <c r="B6" t="n">
-        <v>58239</v>
+        <v>57713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,20 +1128,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>103008</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1144,29 +1149,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338059</v>
+        <v>338112</v>
       </c>
       <c r="R6" t="n">
-        <v>6396360</v>
+        <v>6396514</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291930</v>
+        <v>122293618</v>
       </c>
       <c r="B5" t="n">
-        <v>58239</v>
+        <v>57713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,20 +1013,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>103008</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1034,29 +1034,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338059</v>
+        <v>338112</v>
       </c>
       <c r="R5" t="n">
-        <v>6396360</v>
+        <v>6396514</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,12 +1075,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,7 +1100,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1116,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293618</v>
+        <v>122291930</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>58239</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,20 +1123,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>208249</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1149,24 +1144,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338112</v>
+        <v>338059</v>
       </c>
       <c r="R6" t="n">
-        <v>6396514</v>
+        <v>6396360</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291889</v>
+        <v>122291953</v>
       </c>
       <c r="B2" t="n">
-        <v>56271</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>106554</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338067</v>
+        <v>338171</v>
       </c>
       <c r="R2" t="n">
-        <v>6396349</v>
+        <v>6396632</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293066</v>
+        <v>122291926</v>
       </c>
       <c r="B3" t="n">
-        <v>58084</v>
+        <v>58243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,15 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,24 +824,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338145</v>
+        <v>338033</v>
       </c>
       <c r="R3" t="n">
-        <v>6396569</v>
+        <v>6396368</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -891,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293944</v>
+        <v>122293066</v>
       </c>
       <c r="B4" t="n">
-        <v>56831</v>
+        <v>58088</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,20 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>103055</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,22 +946,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338069</v>
+        <v>338145</v>
       </c>
       <c r="R4" t="n">
-        <v>6396358</v>
+        <v>6396569</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293618</v>
+        <v>122291889</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>56275</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,41 +1037,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338112</v>
+        <v>338067</v>
       </c>
       <c r="R5" t="n">
-        <v>6396514</v>
+        <v>6396349</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,12 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,7 +1121,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1111,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291930</v>
+        <v>122291911</v>
       </c>
       <c r="B6" t="n">
-        <v>58239</v>
+        <v>56275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,35 +1144,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1160,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338059</v>
+        <v>338057</v>
       </c>
       <c r="R6" t="n">
-        <v>6396360</v>
+        <v>6396357</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291911</v>
+        <v>122291892</v>
       </c>
       <c r="B7" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,6 +1261,11 @@
       <c r="E7" t="n">
         <v>205998</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -1262,17 +1284,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338057</v>
+        <v>338212</v>
       </c>
       <c r="R7" t="n">
-        <v>6396357</v>
+        <v>6396580</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,12 +1318,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1343,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1332,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293055</v>
+        <v>122293944</v>
       </c>
       <c r="B8" t="n">
-        <v>58084</v>
+        <v>56835</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,20 +1366,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>102954</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1367,22 +1394,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338165</v>
+        <v>338069</v>
       </c>
       <c r="R8" t="n">
-        <v>6396568</v>
+        <v>6396358</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,12 +1433,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291890</v>
+        <v>122293038</v>
       </c>
       <c r="B9" t="n">
-        <v>56271</v>
+        <v>58088</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,37 +1485,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338032</v>
+        <v>338150</v>
       </c>
       <c r="R9" t="n">
-        <v>6396372</v>
+        <v>6396559</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1548,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122293941</v>
+        <v>122293806</v>
       </c>
       <c r="B10" t="n">
-        <v>56831</v>
+        <v>57925</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,11 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102954</v>
+        <v>102990</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1592,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338163</v>
+        <v>338130</v>
       </c>
       <c r="R10" t="n">
-        <v>6396611</v>
+        <v>6396548</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1622,12 +1663,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293806</v>
+        <v>122291912</v>
       </c>
       <c r="B11" t="n">
-        <v>57921</v>
+        <v>56275</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,45 +1711,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>205998</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338130</v>
+        <v>338034</v>
       </c>
       <c r="R11" t="n">
-        <v>6396548</v>
+        <v>6396372</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,12 +1774,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,7 +1799,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1768,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291926</v>
+        <v>122293941</v>
       </c>
       <c r="B12" t="n">
-        <v>58239</v>
+        <v>56835</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,16 +1826,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>102954</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1801,29 +1848,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338033</v>
+        <v>338163</v>
       </c>
       <c r="R12" t="n">
-        <v>6396368</v>
+        <v>6396611</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,12 +1889,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,7 +1914,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1883,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122293038</v>
+        <v>122293618</v>
       </c>
       <c r="B13" t="n">
-        <v>58084</v>
+        <v>57717</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,16 +1941,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103008</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1927,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338150</v>
+        <v>338112</v>
       </c>
       <c r="R13" t="n">
-        <v>6396559</v>
+        <v>6396514</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1957,12 +2004,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291892</v>
+        <v>122291930</v>
       </c>
       <c r="B14" t="n">
-        <v>56271</v>
+        <v>58243</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,41 +2052,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>208249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338212</v>
+        <v>338059</v>
       </c>
       <c r="R14" t="n">
-        <v>6396580</v>
+        <v>6396360</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,12 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2149,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2099,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291912</v>
+        <v>122291890</v>
       </c>
       <c r="B15" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2117,6 +2178,11 @@
       <c r="E15" t="n">
         <v>205998</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -2139,7 +2205,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338034</v>
+        <v>338032</v>
       </c>
       <c r="R15" t="n">
         <v>6396372</v>
@@ -2169,12 +2235,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,7 +2260,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2205,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291953</v>
+        <v>122293055</v>
       </c>
       <c r="B16" t="n">
-        <v>8430</v>
+        <v>58088</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,26 +2283,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>103055</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2245,13 +2320,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338171</v>
+        <v>338165</v>
       </c>
       <c r="R16" t="n">
-        <v>6396632</v>
+        <v>6396568</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,7 +2375,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291953</v>
+        <v>122291912</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>56275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338171</v>
+        <v>338034</v>
       </c>
       <c r="R2" t="n">
-        <v>6396632</v>
+        <v>6396372</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291926</v>
+        <v>122293618</v>
       </c>
       <c r="B3" t="n">
-        <v>58243</v>
+        <v>57717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,29 +824,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338033</v>
+        <v>338112</v>
       </c>
       <c r="R3" t="n">
-        <v>6396368</v>
+        <v>6396514</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -906,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293066</v>
+        <v>122291911</v>
       </c>
       <c r="B4" t="n">
-        <v>58088</v>
+        <v>56275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,46 +917,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338145</v>
+        <v>338057</v>
       </c>
       <c r="R4" t="n">
-        <v>6396569</v>
+        <v>6396357</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1021,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291889</v>
+        <v>122291930</v>
       </c>
       <c r="B5" t="n">
-        <v>56275</v>
+        <v>58243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1024,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338067</v>
+        <v>338059</v>
       </c>
       <c r="R5" t="n">
-        <v>6396349</v>
+        <v>6396360</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291911</v>
+        <v>122291953</v>
       </c>
       <c r="B6" t="n">
-        <v>56275</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,43 +1144,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338057</v>
+        <v>338171</v>
       </c>
       <c r="R6" t="n">
-        <v>6396357</v>
+        <v>6396632</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291892</v>
+        <v>122291926</v>
       </c>
       <c r="B7" t="n">
-        <v>56275</v>
+        <v>58243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,46 +1255,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338212</v>
+        <v>338033</v>
       </c>
       <c r="R7" t="n">
-        <v>6396580</v>
+        <v>6396368</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,12 +1327,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293944</v>
+        <v>122293055</v>
       </c>
       <c r="B8" t="n">
-        <v>56835</v>
+        <v>58088</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,25 +1375,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,22 +1403,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338069</v>
+        <v>338165</v>
       </c>
       <c r="R8" t="n">
-        <v>6396358</v>
+        <v>6396568</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,12 +1442,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293038</v>
+        <v>122293941</v>
       </c>
       <c r="B9" t="n">
-        <v>58088</v>
+        <v>56835</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1518,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338150</v>
+        <v>338163</v>
       </c>
       <c r="R9" t="n">
-        <v>6396559</v>
+        <v>6396611</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1548,12 +1557,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122293806</v>
+        <v>122291890</v>
       </c>
       <c r="B10" t="n">
-        <v>57925</v>
+        <v>56275</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,50 +1605,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338130</v>
+        <v>338032</v>
       </c>
       <c r="R10" t="n">
-        <v>6396548</v>
+        <v>6396372</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,12 +1668,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1693,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1699,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291912</v>
+        <v>122293806</v>
       </c>
       <c r="B11" t="n">
-        <v>56275</v>
+        <v>57925</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,46 +1716,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338034</v>
+        <v>338130</v>
       </c>
       <c r="R11" t="n">
-        <v>6396372</v>
+        <v>6396548</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,12 +1783,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,7 +1808,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1810,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293941</v>
+        <v>122293066</v>
       </c>
       <c r="B12" t="n">
-        <v>56835</v>
+        <v>58088</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,25 +1831,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1859,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338163</v>
+        <v>338145</v>
       </c>
       <c r="R12" t="n">
-        <v>6396611</v>
+        <v>6396569</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1889,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122293618</v>
+        <v>122291889</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>56275</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,46 +1950,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103008</v>
+        <v>205998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338112</v>
+        <v>338067</v>
       </c>
       <c r="R13" t="n">
-        <v>6396514</v>
+        <v>6396349</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,12 +2009,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2034,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2040,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291930</v>
+        <v>122291892</v>
       </c>
       <c r="B14" t="n">
-        <v>58243</v>
+        <v>56275</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,55 +2057,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338059</v>
+        <v>338212</v>
       </c>
       <c r="R14" t="n">
-        <v>6396360</v>
+        <v>6396580</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,12 +2120,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,7 +2145,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2160,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291890</v>
+        <v>122293038</v>
       </c>
       <c r="B15" t="n">
-        <v>56275</v>
+        <v>58088</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,42 +2172,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338032</v>
+        <v>338150</v>
       </c>
       <c r="R15" t="n">
-        <v>6396372</v>
+        <v>6396559</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122293055</v>
+        <v>122293944</v>
       </c>
       <c r="B16" t="n">
-        <v>58088</v>
+        <v>56835</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2311,22 +2311,22 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338165</v>
+        <v>338069</v>
       </c>
       <c r="R16" t="n">
-        <v>6396568</v>
+        <v>6396358</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293806</v>
+        <v>122293066</v>
       </c>
       <c r="B11" t="n">
-        <v>57925</v>
+        <v>58088</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338130</v>
+        <v>338145</v>
       </c>
       <c r="R11" t="n">
-        <v>6396548</v>
+        <v>6396569</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293066</v>
+        <v>122293806</v>
       </c>
       <c r="B12" t="n">
-        <v>58088</v>
+        <v>57925</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338145</v>
+        <v>338130</v>
       </c>
       <c r="R12" t="n">
-        <v>6396569</v>
+        <v>6396548</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291912</v>
+        <v>122293618</v>
       </c>
       <c r="B2" t="n">
-        <v>56275</v>
+        <v>57717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338034</v>
+        <v>338112</v>
       </c>
       <c r="R2" t="n">
-        <v>6396372</v>
+        <v>6396514</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293618</v>
+        <v>122293066</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>58088</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338112</v>
+        <v>338145</v>
       </c>
       <c r="R3" t="n">
-        <v>6396514</v>
+        <v>6396569</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -865,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291911</v>
+        <v>122293055</v>
       </c>
       <c r="B4" t="n">
-        <v>56275</v>
+        <v>58088</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,42 +921,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338057</v>
+        <v>338165</v>
       </c>
       <c r="R4" t="n">
-        <v>6396357</v>
+        <v>6396568</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1009,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291930</v>
+        <v>122293944</v>
       </c>
       <c r="B5" t="n">
-        <v>58243</v>
+        <v>56835</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1050,14 +1058,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338059</v>
+        <v>338069</v>
       </c>
       <c r="R5" t="n">
-        <v>6396360</v>
+        <v>6396358</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1124,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1132,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291953</v>
+        <v>122293038</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>58088</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,31 +1147,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,13 +1184,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338171</v>
+        <v>338150</v>
       </c>
       <c r="R6" t="n">
-        <v>6396632</v>
+        <v>6396559</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1239,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1243,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291926</v>
+        <v>122291911</v>
       </c>
       <c r="B7" t="n">
-        <v>58243</v>
+        <v>56275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,40 +1262,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,13 +1295,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338033</v>
+        <v>338057</v>
       </c>
       <c r="R7" t="n">
-        <v>6396368</v>
+        <v>6396357</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,12 +1325,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1350,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1363,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293055</v>
+        <v>122293941</v>
       </c>
       <c r="B8" t="n">
-        <v>58088</v>
+        <v>56835</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,25 +1373,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1412,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338165</v>
+        <v>338163</v>
       </c>
       <c r="R8" t="n">
-        <v>6396568</v>
+        <v>6396611</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1442,12 +1440,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293941</v>
+        <v>122291926</v>
       </c>
       <c r="B9" t="n">
-        <v>56835</v>
+        <v>58243</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,21 +1492,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102954</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,24 +1514,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338163</v>
+        <v>338033</v>
       </c>
       <c r="R9" t="n">
-        <v>6396611</v>
+        <v>6396368</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,12 +1560,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,7 +1585,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1593,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291890</v>
+        <v>122291930</v>
       </c>
       <c r="B10" t="n">
-        <v>56275</v>
+        <v>58243</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,31 +1608,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1638,13 +1650,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338032</v>
+        <v>338059</v>
       </c>
       <c r="R10" t="n">
-        <v>6396372</v>
+        <v>6396360</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,12 +1680,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1705,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1704,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293066</v>
+        <v>122293806</v>
       </c>
       <c r="B11" t="n">
-        <v>58088</v>
+        <v>57925</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,25 +1728,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1753,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338145</v>
+        <v>338130</v>
       </c>
       <c r="R11" t="n">
-        <v>6396569</v>
+        <v>6396548</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1783,12 +1795,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293806</v>
+        <v>122291890</v>
       </c>
       <c r="B12" t="n">
-        <v>57925</v>
+        <v>56275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,50 +1843,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338130</v>
+        <v>338032</v>
       </c>
       <c r="R12" t="n">
-        <v>6396548</v>
+        <v>6396372</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,12 +1906,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,7 +1931,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1934,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291889</v>
+        <v>122291953</v>
       </c>
       <c r="B13" t="n">
-        <v>56275</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,46 +1954,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338067</v>
+        <v>338171</v>
       </c>
       <c r="R13" t="n">
-        <v>6396349</v>
+        <v>6396632</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,12 +2017,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,7 +2042,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2045,7 +2053,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291892</v>
+        <v>122291912</v>
       </c>
       <c r="B14" t="n">
         <v>56275</v>
@@ -2086,17 +2094,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338212</v>
+        <v>338034</v>
       </c>
       <c r="R14" t="n">
-        <v>6396580</v>
+        <v>6396372</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2120,12 +2128,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,7 +2153,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2156,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122293038</v>
+        <v>122291889</v>
       </c>
       <c r="B15" t="n">
-        <v>58088</v>
+        <v>56275</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,46 +2180,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338150</v>
+        <v>338067</v>
       </c>
       <c r="R15" t="n">
-        <v>6396559</v>
+        <v>6396349</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2235,12 +2239,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,7 +2264,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2271,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122293944</v>
+        <v>122291892</v>
       </c>
       <c r="B16" t="n">
-        <v>56835</v>
+        <v>56275</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,50 +2287,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338069</v>
+        <v>338212</v>
       </c>
       <c r="R16" t="n">
-        <v>6396358</v>
+        <v>6396580</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293618</v>
+        <v>122293066</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>58088</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338112</v>
+        <v>338145</v>
       </c>
       <c r="R2" t="n">
-        <v>6396514</v>
+        <v>6396569</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293066</v>
+        <v>122293618</v>
       </c>
       <c r="B3" t="n">
-        <v>58088</v>
+        <v>57717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338145</v>
+        <v>338112</v>
       </c>
       <c r="R3" t="n">
-        <v>6396569</v>
+        <v>6396514</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291911</v>
+        <v>122291926</v>
       </c>
       <c r="B7" t="n">
-        <v>56275</v>
+        <v>58243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,31 +1262,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1295,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338057</v>
+        <v>338033</v>
       </c>
       <c r="R7" t="n">
-        <v>6396357</v>
+        <v>6396368</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,12 +1334,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1359,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1361,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293941</v>
+        <v>122291930</v>
       </c>
       <c r="B8" t="n">
-        <v>56835</v>
+        <v>58243</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1399,24 +1408,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338163</v>
+        <v>338059</v>
       </c>
       <c r="R8" t="n">
-        <v>6396611</v>
+        <v>6396360</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,12 +1454,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,7 +1479,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1476,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291926</v>
+        <v>122293941</v>
       </c>
       <c r="B9" t="n">
-        <v>58243</v>
+        <v>56835</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,21 +1506,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>102954</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1514,29 +1528,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338033</v>
+        <v>338163</v>
       </c>
       <c r="R9" t="n">
-        <v>6396368</v>
+        <v>6396611</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,12 +1569,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1594,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1596,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291930</v>
+        <v>122291911</v>
       </c>
       <c r="B10" t="n">
-        <v>58243</v>
+        <v>56275</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,40 +1617,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1650,13 +1650,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338059</v>
+        <v>338057</v>
       </c>
       <c r="R10" t="n">
-        <v>6396360</v>
+        <v>6396357</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293066</v>
+        <v>122291890</v>
       </c>
       <c r="B2" t="n">
-        <v>58088</v>
+        <v>56275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338145</v>
+        <v>338032</v>
       </c>
       <c r="R2" t="n">
-        <v>6396569</v>
+        <v>6396372</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293618</v>
+        <v>122291953</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>8430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338112</v>
+        <v>338171</v>
       </c>
       <c r="R3" t="n">
-        <v>6396514</v>
+        <v>6396632</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293055</v>
+        <v>122293941</v>
       </c>
       <c r="B4" t="n">
-        <v>58088</v>
+        <v>56835</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338165</v>
+        <v>338163</v>
       </c>
       <c r="R4" t="n">
-        <v>6396568</v>
+        <v>6396611</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -984,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293944</v>
+        <v>122293055</v>
       </c>
       <c r="B5" t="n">
-        <v>56835</v>
+        <v>58088</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1024,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,22 +1052,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338069</v>
+        <v>338165</v>
       </c>
       <c r="R5" t="n">
-        <v>6396358</v>
+        <v>6396568</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293038</v>
+        <v>122291930</v>
       </c>
       <c r="B6" t="n">
-        <v>58088</v>
+        <v>58243</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,20 +1139,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,24 +1165,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338150</v>
+        <v>338059</v>
       </c>
       <c r="R6" t="n">
-        <v>6396559</v>
+        <v>6396360</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,12 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1236,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1250,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291926</v>
+        <v>122293066</v>
       </c>
       <c r="B7" t="n">
-        <v>58243</v>
+        <v>58088</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,20 +1259,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1288,29 +1285,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338033</v>
+        <v>338145</v>
       </c>
       <c r="R7" t="n">
-        <v>6396368</v>
+        <v>6396569</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,12 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,7 +1351,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1370,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291930</v>
+        <v>122291926</v>
       </c>
       <c r="B8" t="n">
         <v>58243</v>
@@ -1415,7 +1407,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1424,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338059</v>
+        <v>338033</v>
       </c>
       <c r="R8" t="n">
-        <v>6396360</v>
+        <v>6396368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1490,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293941</v>
+        <v>122293806</v>
       </c>
       <c r="B9" t="n">
-        <v>56835</v>
+        <v>57925</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,16 +1498,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1539,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338163</v>
+        <v>338130</v>
       </c>
       <c r="R9" t="n">
-        <v>6396611</v>
+        <v>6396548</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1569,12 +1561,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291911</v>
+        <v>122291912</v>
       </c>
       <c r="B10" t="n">
         <v>56275</v>
@@ -1650,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338057</v>
+        <v>338034</v>
       </c>
       <c r="R10" t="n">
-        <v>6396357</v>
+        <v>6396372</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1716,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293806</v>
+        <v>122291911</v>
       </c>
       <c r="B11" t="n">
-        <v>57925</v>
+        <v>56275</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,50 +1720,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338130</v>
+        <v>338057</v>
       </c>
       <c r="R11" t="n">
-        <v>6396548</v>
+        <v>6396357</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,12 +1783,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1808,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1831,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291890</v>
+        <v>122293038</v>
       </c>
       <c r="B12" t="n">
-        <v>56275</v>
+        <v>58088</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,42 +1835,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338032</v>
+        <v>338150</v>
       </c>
       <c r="R12" t="n">
-        <v>6396372</v>
+        <v>6396559</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,7 +1923,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1942,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291953</v>
+        <v>122291892</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>56275</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,31 +1946,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>205998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1987,13 +1979,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338171</v>
+        <v>338212</v>
       </c>
       <c r="R13" t="n">
-        <v>6396632</v>
+        <v>6396580</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,12 +2009,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,7 +2034,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2053,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291912</v>
+        <v>122293618</v>
       </c>
       <c r="B14" t="n">
-        <v>56275</v>
+        <v>57717</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,42 +2061,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>103008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338034</v>
+        <v>338112</v>
       </c>
       <c r="R14" t="n">
-        <v>6396372</v>
+        <v>6396514</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,12 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,7 +2149,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2275,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291892</v>
+        <v>122293944</v>
       </c>
       <c r="B16" t="n">
-        <v>56275</v>
+        <v>56835</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,46 +2283,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338212</v>
+        <v>338069</v>
       </c>
       <c r="R16" t="n">
-        <v>6396580</v>
+        <v>6396358</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291890</v>
+        <v>122293066</v>
       </c>
       <c r="B2" t="n">
-        <v>56275</v>
+        <v>58088</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338032</v>
+        <v>338145</v>
       </c>
       <c r="R2" t="n">
-        <v>6396372</v>
+        <v>6396569</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291953</v>
+        <v>122291926</v>
       </c>
       <c r="B3" t="n">
-        <v>8430</v>
+        <v>58243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,42 +806,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338171</v>
+        <v>338033</v>
       </c>
       <c r="R3" t="n">
-        <v>6396632</v>
+        <v>6396368</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293941</v>
+        <v>122291890</v>
       </c>
       <c r="B4" t="n">
-        <v>56835</v>
+        <v>56275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,50 +922,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338163</v>
+        <v>338032</v>
       </c>
       <c r="R4" t="n">
-        <v>6396611</v>
+        <v>6396372</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293055</v>
+        <v>122293618</v>
       </c>
       <c r="B5" t="n">
-        <v>58088</v>
+        <v>57717</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338165</v>
+        <v>338112</v>
       </c>
       <c r="R5" t="n">
-        <v>6396568</v>
+        <v>6396514</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1127,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291930</v>
+        <v>122293806</v>
       </c>
       <c r="B6" t="n">
-        <v>58243</v>
+        <v>57925</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,29 +1174,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338059</v>
+        <v>338130</v>
       </c>
       <c r="R6" t="n">
-        <v>6396360</v>
+        <v>6396548</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1247,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293066</v>
+        <v>122293038</v>
       </c>
       <c r="B7" t="n">
         <v>58088</v>
@@ -1296,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338145</v>
+        <v>338150</v>
       </c>
       <c r="R7" t="n">
-        <v>6396569</v>
+        <v>6396559</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1326,12 +1330,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291926</v>
+        <v>122293055</v>
       </c>
       <c r="B8" t="n">
-        <v>58243</v>
+        <v>58088</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,20 +1378,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,29 +1404,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338033</v>
+        <v>338165</v>
       </c>
       <c r="R8" t="n">
-        <v>6396368</v>
+        <v>6396568</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1445,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1470,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1482,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293806</v>
+        <v>122291892</v>
       </c>
       <c r="B9" t="n">
-        <v>57925</v>
+        <v>56275</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,35 +1493,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1531,13 +1526,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338130</v>
+        <v>338212</v>
       </c>
       <c r="R9" t="n">
-        <v>6396548</v>
+        <v>6396580</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,12 +1556,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1581,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1597,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291912</v>
+        <v>122291930</v>
       </c>
       <c r="B10" t="n">
-        <v>56275</v>
+        <v>58243</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,31 +1604,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1642,13 +1646,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338034</v>
+        <v>338059</v>
       </c>
       <c r="R10" t="n">
-        <v>6396372</v>
+        <v>6396360</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291911</v>
+        <v>122291889</v>
       </c>
       <c r="B11" t="n">
         <v>56275</v>
@@ -1753,13 +1757,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338057</v>
+        <v>338067</v>
       </c>
       <c r="R11" t="n">
-        <v>6396357</v>
+        <v>6396349</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,12 +1787,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1812,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1819,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122293038</v>
+        <v>122291912</v>
       </c>
       <c r="B12" t="n">
-        <v>58088</v>
+        <v>56275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,46 +1839,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338150</v>
+        <v>338034</v>
       </c>
       <c r="R12" t="n">
-        <v>6396559</v>
+        <v>6396372</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291892</v>
+        <v>122291911</v>
       </c>
       <c r="B13" t="n">
         <v>56275</v>
@@ -1975,17 +1975,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338212</v>
+        <v>338057</v>
       </c>
       <c r="R13" t="n">
-        <v>6396580</v>
+        <v>6396357</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122293618</v>
+        <v>122293944</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>56835</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,20 +2057,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103008</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338112</v>
+        <v>338069</v>
       </c>
       <c r="R14" t="n">
-        <v>6396514</v>
+        <v>6396358</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291889</v>
+        <v>122293941</v>
       </c>
       <c r="B15" t="n">
-        <v>56275</v>
+        <v>56835</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,46 +2172,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338067</v>
+        <v>338163</v>
       </c>
       <c r="R15" t="n">
-        <v>6396349</v>
+        <v>6396611</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2235,12 +2239,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,7 +2264,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2271,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122293944</v>
+        <v>122291953</v>
       </c>
       <c r="B16" t="n">
-        <v>56835</v>
+        <v>8430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,46 +2291,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338069</v>
+        <v>338171</v>
       </c>
       <c r="R16" t="n">
-        <v>6396358</v>
+        <v>6396632</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293066</v>
+        <v>122293941</v>
       </c>
       <c r="B2" t="n">
-        <v>58088</v>
+        <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338145</v>
+        <v>338163</v>
       </c>
       <c r="R2" t="n">
-        <v>6396569</v>
+        <v>6396611</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +793,7 @@
         <v>122291926</v>
       </c>
       <c r="B3" t="n">
-        <v>58243</v>
+        <v>58244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291890</v>
+        <v>122291889</v>
       </c>
       <c r="B4" t="n">
-        <v>56275</v>
+        <v>56276</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338032</v>
+        <v>338067</v>
       </c>
       <c r="R4" t="n">
-        <v>6396372</v>
+        <v>6396349</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293618</v>
+        <v>122293038</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>58089</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338112</v>
+        <v>338150</v>
       </c>
       <c r="R5" t="n">
-        <v>6396514</v>
+        <v>6396559</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293806</v>
+        <v>122291892</v>
       </c>
       <c r="B6" t="n">
-        <v>57925</v>
+        <v>56276</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,35 +1148,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338130</v>
+        <v>338212</v>
       </c>
       <c r="R6" t="n">
-        <v>6396548</v>
+        <v>6396580</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,12 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1236,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1251,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293038</v>
+        <v>122291911</v>
       </c>
       <c r="B7" t="n">
-        <v>58088</v>
+        <v>56276</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,46 +1263,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338150</v>
+        <v>338057</v>
       </c>
       <c r="R7" t="n">
-        <v>6396559</v>
+        <v>6396357</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,12 +1322,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1347,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1366,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293055</v>
+        <v>122291890</v>
       </c>
       <c r="B8" t="n">
-        <v>58088</v>
+        <v>56276</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,46 +1374,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338165</v>
+        <v>338032</v>
       </c>
       <c r="R8" t="n">
-        <v>6396568</v>
+        <v>6396372</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,12 +1433,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,7 +1458,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1481,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291892</v>
+        <v>122293618</v>
       </c>
       <c r="B9" t="n">
-        <v>56275</v>
+        <v>57718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,27 +1485,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338212</v>
+        <v>338112</v>
       </c>
       <c r="R9" t="n">
-        <v>6396580</v>
+        <v>6396514</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1592,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291930</v>
+        <v>122293066</v>
       </c>
       <c r="B10" t="n">
-        <v>58243</v>
+        <v>58089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,20 +1596,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1630,29 +1622,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338059</v>
+        <v>338145</v>
       </c>
       <c r="R10" t="n">
-        <v>6396360</v>
+        <v>6396569</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,12 +1663,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,7 +1688,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1712,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291889</v>
+        <v>122293944</v>
       </c>
       <c r="B11" t="n">
-        <v>56275</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,31 +1711,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1757,13 +1748,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338067</v>
+        <v>338069</v>
       </c>
       <c r="R11" t="n">
-        <v>6396349</v>
+        <v>6396358</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1787,12 +1778,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,7 +1803,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1826,7 +1817,7 @@
         <v>122291912</v>
       </c>
       <c r="B12" t="n">
-        <v>56275</v>
+        <v>56276</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291911</v>
+        <v>122291953</v>
       </c>
       <c r="B13" t="n">
-        <v>56275</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,43 +1937,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338057</v>
+        <v>338171</v>
       </c>
       <c r="R13" t="n">
-        <v>6396357</v>
+        <v>6396632</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2009,12 +2000,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122293944</v>
+        <v>122293055</v>
       </c>
       <c r="B14" t="n">
-        <v>56835</v>
+        <v>58089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,25 +2048,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2085,22 +2076,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338069</v>
+        <v>338165</v>
       </c>
       <c r="R14" t="n">
-        <v>6396358</v>
+        <v>6396568</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,12 +2115,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122293941</v>
+        <v>122293806</v>
       </c>
       <c r="B15" t="n">
-        <v>56835</v>
+        <v>57926</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,16 +2167,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2209,10 +2200,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338163</v>
+        <v>338130</v>
       </c>
       <c r="R15" t="n">
-        <v>6396611</v>
+        <v>6396548</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2239,12 +2230,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291953</v>
+        <v>122291930</v>
       </c>
       <c r="B16" t="n">
-        <v>8430</v>
+        <v>58244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,42 +2282,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338171</v>
+        <v>338059</v>
       </c>
       <c r="R16" t="n">
-        <v>6396632</v>
+        <v>6396360</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122293066</v>
+        <v>122293944</v>
       </c>
       <c r="B10" t="n">
-        <v>58089</v>
+        <v>56836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,25 +1596,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1624,22 +1624,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338145</v>
+        <v>338069</v>
       </c>
       <c r="R10" t="n">
-        <v>6396569</v>
+        <v>6396358</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293944</v>
+        <v>122293066</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
+        <v>58089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,25 +1711,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1739,22 +1739,22 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338069</v>
+        <v>338145</v>
       </c>
       <c r="R11" t="n">
-        <v>6396358</v>
+        <v>6396569</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293941</v>
+        <v>122293066</v>
       </c>
       <c r="B2" t="n">
-        <v>56836</v>
+        <v>58089</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338163</v>
+        <v>338145</v>
       </c>
       <c r="R2" t="n">
-        <v>6396611</v>
+        <v>6396569</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -910,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291889</v>
+        <v>122291892</v>
       </c>
       <c r="B4" t="n">
         <v>56276</v>
@@ -951,14 +951,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338067</v>
+        <v>338212</v>
       </c>
       <c r="R4" t="n">
-        <v>6396349</v>
+        <v>6396580</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293038</v>
+        <v>122293941</v>
       </c>
       <c r="B5" t="n">
-        <v>58089</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338150</v>
+        <v>338163</v>
       </c>
       <c r="R5" t="n">
-        <v>6396559</v>
+        <v>6396611</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291892</v>
+        <v>122291912</v>
       </c>
       <c r="B6" t="n">
         <v>56276</v>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338212</v>
+        <v>338034</v>
       </c>
       <c r="R6" t="n">
-        <v>6396580</v>
+        <v>6396372</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291911</v>
+        <v>122291953</v>
       </c>
       <c r="B7" t="n">
-        <v>56276</v>
+        <v>8430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,43 +1259,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338057</v>
+        <v>338171</v>
       </c>
       <c r="R7" t="n">
-        <v>6396357</v>
+        <v>6396632</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122293066</v>
+        <v>122291911</v>
       </c>
       <c r="B11" t="n">
-        <v>58089</v>
+        <v>56276</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,46 +1715,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338145</v>
+        <v>338057</v>
       </c>
       <c r="R11" t="n">
-        <v>6396569</v>
+        <v>6396357</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,12 +1774,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1799,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1814,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291912</v>
+        <v>122291930</v>
       </c>
       <c r="B12" t="n">
-        <v>56276</v>
+        <v>58244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,31 +1822,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1859,13 +1864,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338034</v>
+        <v>338059</v>
       </c>
       <c r="R12" t="n">
-        <v>6396372</v>
+        <v>6396360</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291953</v>
+        <v>122293806</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>57926</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,27 +1946,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1970,13 +1979,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338171</v>
+        <v>338130</v>
       </c>
       <c r="R13" t="n">
-        <v>6396632</v>
+        <v>6396548</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2000,12 +2009,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,7 +2034,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2151,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122293806</v>
+        <v>122293038</v>
       </c>
       <c r="B15" t="n">
-        <v>57926</v>
+        <v>58089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2163,25 +2172,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2200,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338130</v>
+        <v>338150</v>
       </c>
       <c r="R15" t="n">
-        <v>6396548</v>
+        <v>6396559</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2230,12 +2239,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291930</v>
+        <v>122291889</v>
       </c>
       <c r="B16" t="n">
-        <v>58244</v>
+        <v>56276</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,40 +2287,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338059</v>
+        <v>338067</v>
       </c>
       <c r="R16" t="n">
-        <v>6396360</v>
+        <v>6396349</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">

--- a/artfynd/A 3655-2021 artfynd.xlsx
+++ b/artfynd/A 3655-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293066</v>
+        <v>122291892</v>
       </c>
       <c r="B2" t="n">
-        <v>58089</v>
+        <v>56276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338145</v>
+        <v>338212</v>
       </c>
       <c r="R2" t="n">
-        <v>6396569</v>
+        <v>6396580</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -910,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291892</v>
+        <v>122291953</v>
       </c>
       <c r="B4" t="n">
-        <v>56276</v>
+        <v>8430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,31 +918,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -955,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338212</v>
+        <v>338171</v>
       </c>
       <c r="R4" t="n">
-        <v>6396580</v>
+        <v>6396632</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1006,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1021,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293941</v>
+        <v>122293055</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
+        <v>58089</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1070,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338163</v>
+        <v>338165</v>
       </c>
       <c r="R5" t="n">
-        <v>6396611</v>
+        <v>6396568</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,12 +1096,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1247,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291953</v>
+        <v>122291930</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>58244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,42 +1259,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338171</v>
+        <v>338059</v>
       </c>
       <c r="R7" t="n">
-        <v>6396632</v>
+        <v>6396360</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,12 +1327,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291890</v>
+        <v>122293944</v>
       </c>
       <c r="B8" t="n">
-        <v>56276</v>
+        <v>56836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,31 +1375,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1403,13 +1412,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338032</v>
+        <v>338069</v>
       </c>
       <c r="R8" t="n">
-        <v>6396372</v>
+        <v>6396358</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,12 +1442,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1467,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1469,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122293618</v>
+        <v>122291889</v>
       </c>
       <c r="B9" t="n">
-        <v>57718</v>
+        <v>56276</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,46 +1494,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103008</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338112</v>
+        <v>338067</v>
       </c>
       <c r="R9" t="n">
-        <v>6396514</v>
+        <v>6396349</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,12 +1553,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,7 +1578,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1584,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122293944</v>
+        <v>122293066</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
+        <v>58089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,25 +1601,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1624,22 +1629,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338069</v>
+        <v>338145</v>
       </c>
       <c r="R10" t="n">
-        <v>6396358</v>
+        <v>6396569</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,12 +1668,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291911</v>
+        <v>122293038</v>
       </c>
       <c r="B11" t="n">
-        <v>56276</v>
+        <v>58089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,42 +1720,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338057</v>
+        <v>338150</v>
       </c>
       <c r="R11" t="n">
-        <v>6396357</v>
+        <v>6396559</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,12 +1783,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,7 +1808,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1810,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291930</v>
+        <v>122293806</v>
       </c>
       <c r="B12" t="n">
-        <v>58244</v>
+        <v>57926</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,21 +1835,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1848,29 +1857,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammtjärnen, Vg</t>
+          <t>Knös, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338059</v>
+        <v>338130</v>
       </c>
       <c r="R12" t="n">
-        <v>6396360</v>
+        <v>6396548</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1894,12 +1898,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,7 +1923,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1930,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122293806</v>
+        <v>122293941</v>
       </c>
       <c r="B13" t="n">
-        <v>57926</v>
+        <v>56836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,16 +1950,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1979,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338130</v>
+        <v>338163</v>
       </c>
       <c r="R13" t="n">
-        <v>6396548</v>
+        <v>6396611</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2009,12 +2013,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122293055</v>
+        <v>122291890</v>
       </c>
       <c r="B14" t="n">
-        <v>58089</v>
+        <v>56276</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,46 +2065,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knös, Vg</t>
+          <t>Dammtjärnen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338165</v>
+        <v>338032</v>
       </c>
       <c r="R14" t="n">
-        <v>6396568</v>
+        <v>6396372</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2160,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122293038</v>
+        <v>122293618</v>
       </c>
       <c r="B15" t="n">
-        <v>58089</v>
+        <v>57718</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,21 +2176,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338150</v>
+        <v>338112</v>
       </c>
       <c r="R15" t="n">
-        <v>6396559</v>
+        <v>6396514</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291889</v>
+        <v>122291911</v>
       </c>
       <c r="B16" t="n">
         <v>56276</v>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338067</v>
+        <v>338057</v>
       </c>
       <c r="R16" t="n">
-        <v>6396349</v>
+        <v>6396357</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
